--- a/Model_Benchmark_Detailed_v2.xlsx
+++ b/Model_Benchmark_Detailed_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\studying\3eme info(DSI33)\PFE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8A8C971-A9FE-467E-974C-FAAD063906FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{265E7997-6E8F-4D6B-BB20-F55E74045F85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
